--- a/宾果数学-Bingo机率与RTP模型.xlsx
+++ b/宾果数学-Bingo机率与RTP模型.xlsx
@@ -6804,6 +6804,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:AX230" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -9791,5 +9794,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N150" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/宾果数学-Bingo机率与RTP模型.xlsx
+++ b/宾果数学-Bingo机率与RTP模型.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="Bingo 机率+赔率→RTP" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1584,7 +1584,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1680,6 +1680,39 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2233,4516 +2266,4516 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" spans="1:11">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
     </row>
     <row r="2" ht="20" spans="1:11">
-      <c r="A2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="24" t="s">
+      <c r="A2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:11">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="24" t="s">
+      <c r="B3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1" spans="1:11">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="24" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:11">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:11">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="24" t="s">
+      <c r="B6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:11">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="24" t="s">
+      <c r="B7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:11">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
     </row>
     <row r="9" ht="16.5" spans="1:11">
-      <c r="A9" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="24" t="s">
+      <c r="A9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:11">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="24" t="s">
+      <c r="B10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="45.75" customHeight="1" spans="1:11">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
     </row>
     <row r="12" ht="30.75" customHeight="1" spans="1:11">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
     </row>
     <row r="13" ht="30.75" customHeight="1" spans="1:11">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
     </row>
     <row r="14" ht="45.75" customHeight="1" spans="1:11">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
     </row>
     <row r="15" ht="16.5" spans="1:11">
-      <c r="A15" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="24" t="s">
+      <c r="A15" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:11">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="24" t="s">
+      <c r="B16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1" spans="1:23">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="24" t="s">
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1" spans="1:23">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="24" t="s">
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" ht="30.75" customHeight="1" spans="1:23">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="24" t="s">
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1" spans="1:23">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:23">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
     </row>
     <row r="22" ht="30.75" customHeight="1" spans="1:23">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
     </row>
     <row r="23" ht="16.5" spans="1:23">
-      <c r="A23" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" s="24" t="s">
+      <c r="A23" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G24" s="24" t="s">
+      <c r="B24" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="30.75" customHeight="1" spans="1:23">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="24" t="s">
+      <c r="B26" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="30.75" customHeight="1" spans="1:23">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" s="24" t="s">
+      <c r="B28" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="45.75" customHeight="1" spans="1:23">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
     </row>
     <row r="30" ht="16.5" spans="1:23">
-      <c r="A30" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="24" t="s">
+      <c r="A30" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="24" t="s">
+      <c r="B31" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:23">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-      <c r="W32" s="27"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="38"/>
+      <c r="S32" s="38"/>
+      <c r="T32" s="38"/>
+      <c r="U32" s="38"/>
+      <c r="V32" s="38"/>
+      <c r="W32" s="38"/>
     </row>
     <row r="33" ht="16.5" spans="1:45">
-      <c r="A33" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="24" t="s">
+      <c r="A33" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:45">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="24" t="s">
+      <c r="B34" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="30.75" customHeight="1" spans="1:45">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="24" t="s">
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:45">
-      <c r="A36" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="24" t="s">
+      <c r="A36" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:45">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="24" t="s">
+      <c r="B37" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:45">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="27"/>
-      <c r="M38" s="27"/>
-      <c r="N38" s="27"/>
-      <c r="O38" s="27"/>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="27"/>
-      <c r="V38" s="27"/>
-      <c r="W38" s="27"/>
-      <c r="X38" s="27"/>
-      <c r="Y38" s="27"/>
-      <c r="Z38" s="27"/>
-      <c r="AA38" s="27"/>
-      <c r="AB38" s="27"/>
-      <c r="AC38" s="27"/>
-      <c r="AD38" s="27"/>
-      <c r="AE38" s="27"/>
-      <c r="AF38" s="27"/>
-      <c r="AG38" s="27"/>
-      <c r="AH38" s="27"/>
-      <c r="AI38" s="27"/>
-      <c r="AJ38" s="27"/>
-      <c r="AK38" s="27"/>
-      <c r="AL38" s="27"/>
-      <c r="AM38" s="27"/>
-      <c r="AN38" s="27"/>
-      <c r="AO38" s="27"/>
-      <c r="AP38" s="27"/>
-      <c r="AQ38" s="27"/>
-      <c r="AR38" s="27"/>
-      <c r="AS38" s="27"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="38"/>
+      <c r="P38" s="38"/>
+      <c r="Q38" s="38"/>
+      <c r="R38" s="38"/>
+      <c r="S38" s="38"/>
+      <c r="T38" s="38"/>
+      <c r="U38" s="38"/>
+      <c r="V38" s="38"/>
+      <c r="W38" s="38"/>
+      <c r="X38" s="38"/>
+      <c r="Y38" s="38"/>
+      <c r="Z38" s="38"/>
+      <c r="AA38" s="38"/>
+      <c r="AB38" s="38"/>
+      <c r="AC38" s="38"/>
+      <c r="AD38" s="38"/>
+      <c r="AE38" s="38"/>
+      <c r="AF38" s="38"/>
+      <c r="AG38" s="38"/>
+      <c r="AH38" s="38"/>
+      <c r="AI38" s="38"/>
+      <c r="AJ38" s="38"/>
+      <c r="AK38" s="38"/>
+      <c r="AL38" s="38"/>
+      <c r="AM38" s="38"/>
+      <c r="AN38" s="38"/>
+      <c r="AO38" s="38"/>
+      <c r="AP38" s="38"/>
+      <c r="AQ38" s="38"/>
+      <c r="AR38" s="38"/>
+      <c r="AS38" s="38"/>
     </row>
     <row r="39" ht="16.5" spans="1:45">
-      <c r="A39" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="24" t="s">
+      <c r="A39" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="17.25" customHeight="1" spans="1:45">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B40" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="24" t="s">
+      <c r="B40" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" ht="20.25" customHeight="1" spans="1:45">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="24" t="s">
+      <c r="B41" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:45">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="24" t="s">
+      <c r="B42" s="40"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" ht="30.75" customHeight="1" spans="1:45">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="24" t="s">
+      <c r="B43" s="40"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:45">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="24" t="s">
+      <c r="B44" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:45">
-      <c r="A45" s="26" t="s">
+      <c r="A45" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="24" t="s">
+      <c r="B45" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:45">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="38"/>
+      <c r="K46" s="38"/>
+      <c r="L46" s="38"/>
+      <c r="M46" s="38"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="38"/>
+      <c r="Q46" s="38"/>
+      <c r="R46" s="38"/>
+      <c r="S46" s="38"/>
     </row>
     <row r="47" ht="17.25" customHeight="1" spans="1:45">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="24" t="s">
+      <c r="B47" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" ht="45.75" customHeight="1" spans="1:45">
-      <c r="A48" s="26" t="s">
+      <c r="A48" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="26"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="37"/>
     </row>
     <row r="49" ht="30.75" customHeight="1" spans="1:7">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="24" t="s">
+      <c r="B49" s="37"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="24" t="s">
+      <c r="B50" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" ht="288" customHeight="1" spans="1:7">
-      <c r="A51" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B51" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" s="24" t="s">
+      <c r="A51" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:7">
-      <c r="A52" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B52" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" s="24" t="s">
+      <c r="A52" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:7">
-      <c r="A53" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B53" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="24" t="s">
+      <c r="A53" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B53" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:7">
-      <c r="A54" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B54" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" s="24" t="s">
+      <c r="A54" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:7">
-      <c r="A55" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B55" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G55" s="24" t="s">
+      <c r="A55" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:7">
-      <c r="A56" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B56" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E56" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G56" s="24" t="s">
+      <c r="A56" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B56" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:7">
-      <c r="A57" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B57" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="24" t="s">
+      <c r="A57" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:7">
-      <c r="A58" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B58" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="24" t="s">
+      <c r="A58" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:7">
-      <c r="A59" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B59" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" s="24" t="s">
+      <c r="A59" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:7">
-      <c r="A60" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="24" t="s">
+      <c r="A60" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B60" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:7">
-      <c r="A61" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="24" t="s">
+      <c r="A61" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B61" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:7">
-      <c r="A62" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C62" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="24" t="s">
+      <c r="A62" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:7">
-      <c r="A63" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B63" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C63" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="24" t="s">
+      <c r="A63" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B63" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:7">
-      <c r="A64" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B64" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G64" s="24" t="s">
+      <c r="A64" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B64" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:19">
-      <c r="A65" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B65" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="24" t="s">
+      <c r="A65" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B65" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:19">
-      <c r="A66" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B66" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D66" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G66" s="24" t="s">
+      <c r="A66" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B66" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:19">
-      <c r="A67" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B67" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D67" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G67" s="24" t="s">
+      <c r="A67" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B67" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:19">
-      <c r="A68" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B68" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G68" s="24" t="s">
+      <c r="A68" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B68" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G68" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:19">
-      <c r="A69" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B69" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E69" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G69" s="24" t="s">
+      <c r="A69" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G69" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:19">
-      <c r="A70" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B70" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C70" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D70" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E70" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G70" s="24" t="s">
+      <c r="A70" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B70" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E70" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G70" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:19">
-      <c r="A71" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B71" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G71" s="24" t="s">
+      <c r="A71" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B71" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E71" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G71" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:19">
-      <c r="A72" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B72" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E72" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G72" s="24" t="s">
+      <c r="A72" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B72" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E72" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G72" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:19">
-      <c r="A73" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B73" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C73" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G73" s="24" t="s">
+      <c r="A73" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B73" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G73" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:19">
-      <c r="A74" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B74" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D74" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E74" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G74" s="24" t="s">
+      <c r="A74" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B74" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E74" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G74" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:19">
-      <c r="A75" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B75" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E75" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G75" s="24" t="s">
+      <c r="A75" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B75" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E75" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="76" ht="17.25" customHeight="1" spans="1:19">
-      <c r="A76" s="28" t="s">
+      <c r="A76" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="B76" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D76" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E76" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G76" s="24" t="s">
+      <c r="B76" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D76" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E76" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G76" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" ht="30.75" customHeight="1" spans="1:19">
-      <c r="A77" s="26" t="s">
+      <c r="A77" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="B77" s="26"/>
-      <c r="C77" s="26"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="26"/>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
-      <c r="H77" s="26"/>
+      <c r="B77" s="37"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37"/>
     </row>
     <row r="78" ht="15" customHeight="1" spans="1:19">
-      <c r="A78" s="27" t="s">
+      <c r="A78" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="27"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="38"/>
+      <c r="H78" s="38"/>
+      <c r="I78" s="38"/>
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:19">
-      <c r="A79" s="27" t="s">
+      <c r="A79" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="27"/>
-      <c r="J79" s="27"/>
-      <c r="K79" s="27"/>
-      <c r="L79" s="27"/>
-      <c r="M79" s="27"/>
-      <c r="N79" s="27"/>
-      <c r="O79" s="27"/>
-      <c r="P79" s="27"/>
-      <c r="Q79" s="27"/>
-      <c r="R79" s="27"/>
-      <c r="S79" s="27"/>
+      <c r="B79" s="38"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="38"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="38"/>
+      <c r="J79" s="38"/>
+      <c r="K79" s="38"/>
+      <c r="L79" s="38"/>
+      <c r="M79" s="38"/>
+      <c r="N79" s="38"/>
+      <c r="O79" s="38"/>
+      <c r="P79" s="38"/>
+      <c r="Q79" s="38"/>
+      <c r="R79" s="38"/>
+      <c r="S79" s="38"/>
     </row>
     <row r="80" ht="17.25" customHeight="1" spans="1:19">
-      <c r="A80" s="28" t="s">
+      <c r="A80" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C80" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D80" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E80" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F80" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G80" s="24" t="s">
+      <c r="B80" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D80" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G80" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" ht="30.75" customHeight="1" spans="1:7">
-      <c r="A81" s="26" t="s">
+      <c r="A81" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="B81" s="26"/>
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F81" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G81" s="24" t="s">
+      <c r="B81" s="37"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="37"/>
+      <c r="E81" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G81" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:7">
-      <c r="A82" s="24" t="s">
+      <c r="A82" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B82" s="24" t="s">
+      <c r="B82" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="C82" s="24" t="s">
+      <c r="C82" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="D82" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E82" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F82" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G82" s="24" t="s">
+      <c r="D82" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E82" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G82" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:7">
-      <c r="A83" s="30" t="s">
+      <c r="A83" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B83" s="31" t="s">
+      <c r="B83" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="C83" s="31" t="s">
+      <c r="C83" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="D83" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E83" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F83" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G83" s="24" t="s">
+      <c r="D83" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E83" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F83" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G83" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1" spans="1:7">
-      <c r="A84" s="30" t="s">
+      <c r="A84" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B84" s="31" t="s">
+      <c r="B84" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="C84" s="31">
+      <c r="C84" s="42">
         <v>15</v>
       </c>
-      <c r="D84" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E84" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F84" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G84" s="24" t="s">
+      <c r="D84" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E84" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G84" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:7">
-      <c r="A85" s="30" t="s">
+      <c r="A85" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="B85" s="31" t="s">
+      <c r="B85" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="C85" s="31" t="s">
+      <c r="C85" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="D85" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F85" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G85" s="24" t="s">
+      <c r="D85" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G85" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:7">
-      <c r="A86" s="30" t="s">
+      <c r="A86" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="B86" s="31" t="s">
+      <c r="B86" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="C86" s="31" t="s">
+      <c r="C86" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="D86" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E86" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F86" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G86" s="24" t="s">
+      <c r="D86" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E86" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G86" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="87" ht="45" customHeight="1" spans="1:7">
-      <c r="A87" s="30" t="s">
+      <c r="A87" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B87" s="31" t="s">
+      <c r="B87" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="C87" s="31" t="s">
+      <c r="C87" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="D87" s="31"/>
-      <c r="E87" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F87" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G87" s="24" t="s">
+      <c r="D87" s="42"/>
+      <c r="E87" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G87" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:7">
-      <c r="A88" s="27" t="s">
+      <c r="A88" s="38" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="89" ht="156.75" customHeight="1" spans="1:7">
-      <c r="A89" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B89" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C89" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D89" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E89" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F89" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G89" s="24" t="s">
+      <c r="A89" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B89" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E89" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G89" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:7">
-      <c r="A90" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B90" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C90" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D90" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E90" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F90" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G90" s="24" t="s">
+      <c r="A90" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B90" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D90" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E90" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G90" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:7">
-      <c r="A91" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B91" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C91" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D91" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E91" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F91" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G91" s="24" t="s">
+      <c r="A91" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B91" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D91" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E91" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F91" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G91" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:7">
-      <c r="A92" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B92" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C92" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D92" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E92" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F92" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G92" s="24" t="s">
+      <c r="A92" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B92" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E92" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G92" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:7">
-      <c r="A93" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B93" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C93" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D93" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E93" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F93" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G93" s="24" t="s">
+      <c r="A93" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B93" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C93" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D93" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E93" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F93" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G93" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:7">
-      <c r="A94" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B94" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C94" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D94" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E94" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F94" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G94" s="24" t="s">
+      <c r="A94" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B94" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C94" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D94" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E94" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G94" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:7">
-      <c r="A95" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B95" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C95" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D95" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E95" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F95" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G95" s="24" t="s">
+      <c r="A95" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B95" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D95" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F95" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G95" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:7">
-      <c r="A96" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B96" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C96" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D96" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E96" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F96" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G96" s="24" t="s">
+      <c r="A96" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B96" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D96" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E96" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G96" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:17">
-      <c r="A97" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B97" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C97" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D97" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E97" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F97" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G97" s="24" t="s">
+      <c r="A97" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B97" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C97" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D97" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E97" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G97" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:17">
-      <c r="A98" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B98" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C98" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D98" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E98" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F98" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G98" s="24" t="s">
+      <c r="A98" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B98" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D98" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E98" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F98" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G98" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:17">
-      <c r="A99" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B99" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C99" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D99" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E99" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F99" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G99" s="24" t="s">
+      <c r="A99" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B99" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D99" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E99" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G99" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:17">
-      <c r="A100" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B100" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C100" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D100" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E100" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F100" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G100" s="24" t="s">
+      <c r="A100" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B100" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D100" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E100" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F100" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G100" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:17">
-      <c r="A101" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B101" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C101" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D101" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E101" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F101" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G101" s="24" t="s">
+      <c r="A101" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B101" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C101" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D101" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E101" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G101" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:17">
-      <c r="A102" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B102" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C102" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D102" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E102" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F102" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G102" s="24" t="s">
+      <c r="A102" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B102" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D102" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E102" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F102" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G102" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="103" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A103" s="26" t="s">
+      <c r="A103" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="B103" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C103" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D103" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E103" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F103" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G103" s="24" t="s">
+      <c r="B103" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D103" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E103" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G103" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:17">
-      <c r="A104" s="24" t="s">
+      <c r="A104" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B104" s="24" t="s">
+      <c r="B104" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C104" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D104" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E104" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F104" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G104" s="24" t="s">
+      <c r="C104" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D104" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E104" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F104" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G104" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:17">
-      <c r="A105" s="30" t="s">
+      <c r="A105" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="B105" s="31" t="s">
+      <c r="B105" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="C105" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D105" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E105" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F105" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G105" s="24" t="s">
+      <c r="C105" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D105" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E105" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F105" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G105" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="106" ht="27.75" customHeight="1" spans="1:17">
-      <c r="A106" s="30" t="s">
+      <c r="A106" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="B106" s="31" t="s">
+      <c r="B106" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C106" s="31"/>
-      <c r="D106" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E106" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F106" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G106" s="24" t="s">
+      <c r="C106" s="42"/>
+      <c r="D106" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E106" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F106" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G106" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:17">
-      <c r="A107" s="30" t="s">
+      <c r="A107" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B107" s="31" t="s">
+      <c r="B107" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C107" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D107" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E107" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F107" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G107" s="24" t="s">
+      <c r="C107" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E107" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F107" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G107" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="108" ht="17.25" customHeight="1" spans="1:17">
-      <c r="A108" s="28" t="s">
+      <c r="A108" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="B108" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C108" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D108" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E108" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F108" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G108" s="24" t="s">
+      <c r="B108" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D108" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E108" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F108" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G108" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:17">
-      <c r="A109" s="27" t="s">
+      <c r="A109" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="B109" s="27"/>
-      <c r="C109" s="27"/>
-      <c r="D109" s="27"/>
-      <c r="E109" s="27"/>
-      <c r="F109" s="27"/>
-      <c r="G109" s="27"/>
-      <c r="H109" s="27"/>
-      <c r="I109" s="27"/>
-      <c r="J109" s="27"/>
-      <c r="K109" s="27"/>
+      <c r="B109" s="38"/>
+      <c r="C109" s="38"/>
+      <c r="D109" s="38"/>
+      <c r="E109" s="38"/>
+      <c r="F109" s="38"/>
+      <c r="G109" s="38"/>
+      <c r="H109" s="38"/>
+      <c r="I109" s="38"/>
+      <c r="J109" s="38"/>
+      <c r="K109" s="38"/>
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:17">
-      <c r="A110" s="27" t="s">
+      <c r="A110" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="B110" s="27"/>
-      <c r="C110" s="27"/>
-      <c r="D110" s="27"/>
-      <c r="E110" s="27"/>
-      <c r="F110" s="27"/>
-      <c r="G110" s="27"/>
-      <c r="H110" s="27"/>
-      <c r="I110" s="27"/>
-      <c r="J110" s="27"/>
-      <c r="K110" s="27"/>
-      <c r="L110" s="27"/>
-      <c r="M110" s="27"/>
-      <c r="N110" s="27"/>
-      <c r="O110" s="27"/>
-      <c r="P110" s="27"/>
-      <c r="Q110" s="27"/>
+      <c r="B110" s="38"/>
+      <c r="C110" s="38"/>
+      <c r="D110" s="38"/>
+      <c r="E110" s="38"/>
+      <c r="F110" s="38"/>
+      <c r="G110" s="38"/>
+      <c r="H110" s="38"/>
+      <c r="I110" s="38"/>
+      <c r="J110" s="38"/>
+      <c r="K110" s="38"/>
+      <c r="L110" s="38"/>
+      <c r="M110" s="38"/>
+      <c r="N110" s="38"/>
+      <c r="O110" s="38"/>
+      <c r="P110" s="38"/>
+      <c r="Q110" s="38"/>
     </row>
     <row r="111" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A111" s="26" t="s">
+      <c r="A111" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="B111" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C111" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D111" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E111" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F111" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G111" s="24" t="s">
+      <c r="B111" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C111" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D111" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E111" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F111" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G111" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="112" ht="375" customHeight="1" spans="1:17">
-      <c r="A112" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B112" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C112" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D112" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E112" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F112" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G112" s="24" t="s">
+      <c r="A112" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B112" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C112" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D112" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E112" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F112" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G112" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="1:7">
-      <c r="A113" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B113" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C113" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D113" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E113" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F113" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G113" s="24" t="s">
+      <c r="A113" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B113" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C113" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D113" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E113" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F113" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G113" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="1:7">
-      <c r="A114" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B114" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C114" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D114" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E114" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F114" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G114" s="24" t="s">
+      <c r="A114" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B114" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C114" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D114" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E114" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F114" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G114" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="115" ht="16.5" spans="1:7">
-      <c r="A115" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B115" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C115" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D115" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E115" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F115" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G115" s="24" t="s">
+      <c r="A115" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B115" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C115" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D115" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E115" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F115" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G115" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="116" ht="16.5" spans="1:7">
-      <c r="A116" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B116" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C116" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D116" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E116" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F116" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G116" s="24" t="s">
+      <c r="A116" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B116" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C116" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D116" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E116" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F116" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G116" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="117" ht="16.5" spans="1:7">
-      <c r="A117" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B117" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C117" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D117" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E117" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F117" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G117" s="24" t="s">
+      <c r="A117" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B117" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C117" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D117" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E117" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F117" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G117" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="1:7">
-      <c r="A118" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B118" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C118" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D118" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E118" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F118" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G118" s="24" t="s">
+      <c r="A118" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B118" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C118" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D118" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E118" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F118" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G118" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="1:7">
-      <c r="A119" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B119" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C119" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D119" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E119" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F119" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G119" s="24" t="s">
+      <c r="A119" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B119" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C119" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D119" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E119" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F119" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G119" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="1:7">
-      <c r="A120" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B120" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C120" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D120" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E120" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F120" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G120" s="24" t="s">
+      <c r="A120" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B120" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C120" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D120" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E120" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F120" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G120" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="121" ht="16.5" spans="1:7">
-      <c r="A121" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B121" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C121" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D121" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E121" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F121" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G121" s="24" t="s">
+      <c r="A121" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B121" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C121" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D121" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E121" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F121" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G121" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="122" ht="16.5" spans="1:7">
-      <c r="A122" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B122" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C122" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D122" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E122" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F122" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G122" s="24" t="s">
+      <c r="A122" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B122" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C122" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D122" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E122" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F122" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G122" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="123" ht="16.5" spans="1:7">
-      <c r="A123" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B123" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C123" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D123" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E123" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F123" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G123" s="24" t="s">
+      <c r="A123" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B123" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D123" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E123" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F123" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G123" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="124" ht="16.5" spans="1:7">
-      <c r="A124" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B124" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C124" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D124" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E124" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F124" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G124" s="24" t="s">
+      <c r="A124" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B124" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C124" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D124" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E124" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F124" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G124" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="1:7">
-      <c r="A125" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B125" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C125" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D125" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E125" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F125" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G125" s="24" t="s">
+      <c r="A125" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B125" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C125" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D125" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E125" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F125" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G125" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="1:7">
-      <c r="A126" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B126" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C126" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D126" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E126" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F126" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G126" s="24" t="s">
+      <c r="A126" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B126" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C126" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D126" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E126" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F126" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G126" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="1:7">
-      <c r="A127" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B127" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C127" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D127" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E127" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F127" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G127" s="24" t="s">
+      <c r="A127" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B127" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C127" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D127" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E127" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F127" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G127" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="1:7">
-      <c r="A128" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B128" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C128" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D128" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E128" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F128" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G128" s="24" t="s">
+      <c r="A128" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B128" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C128" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D128" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E128" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F128" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G128" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="1:7">
-      <c r="A129" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B129" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C129" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D129" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E129" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F129" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G129" s="24" t="s">
+      <c r="A129" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B129" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C129" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D129" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E129" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F129" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G129" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="1:7">
-      <c r="A130" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B130" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C130" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D130" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E130" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F130" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G130" s="24" t="s">
+      <c r="A130" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B130" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C130" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D130" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E130" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F130" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G130" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="1:7">
-      <c r="A131" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B131" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C131" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D131" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E131" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F131" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G131" s="24" t="s">
+      <c r="A131" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B131" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C131" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D131" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E131" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F131" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G131" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="1:7">
-      <c r="A132" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B132" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C132" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D132" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E132" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F132" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G132" s="24" t="s">
+      <c r="A132" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B132" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C132" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D132" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E132" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F132" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G132" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="1:7">
-      <c r="A133" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B133" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C133" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D133" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E133" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F133" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G133" s="24" t="s">
+      <c r="A133" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B133" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C133" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D133" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E133" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F133" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G133" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="1:7">
-      <c r="A134" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B134" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C134" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D134" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E134" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F134" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G134" s="24" t="s">
+      <c r="A134" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B134" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C134" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D134" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E134" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F134" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G134" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="1:7">
-      <c r="A135" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B135" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C135" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D135" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E135" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F135" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G135" s="24" t="s">
+      <c r="A135" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B135" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C135" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D135" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E135" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F135" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G135" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="1:7">
-      <c r="A136" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B136" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C136" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D136" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E136" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F136" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G136" s="24" t="s">
+      <c r="A136" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B136" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C136" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D136" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E136" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F136" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G136" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="1:7">
-      <c r="A137" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B137" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C137" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D137" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E137" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F137" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G137" s="24" t="s">
+      <c r="A137" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B137" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C137" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D137" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E137" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F137" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G137" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="1:7">
-      <c r="A138" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B138" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C138" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D138" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E138" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F138" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G138" s="24" t="s">
+      <c r="A138" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B138" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C138" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D138" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E138" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F138" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G138" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="139" ht="16.5" spans="1:7">
-      <c r="A139" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B139" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C139" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D139" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E139" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F139" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G139" s="24" t="s">
+      <c r="A139" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B139" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C139" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D139" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E139" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F139" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G139" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="140" ht="16.5" spans="1:7">
-      <c r="A140" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B140" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C140" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D140" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E140" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F140" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G140" s="24" t="s">
+      <c r="A140" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B140" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C140" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D140" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E140" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F140" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G140" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="1:7">
-      <c r="A141" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B141" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C141" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D141" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E141" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F141" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G141" s="24" t="s">
+      <c r="A141" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B141" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C141" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D141" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E141" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F141" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G141" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="1:7">
-      <c r="A142" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B142" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C142" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D142" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E142" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F142" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G142" s="24" t="s">
+      <c r="A142" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B142" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C142" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D142" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E142" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F142" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G142" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="1:7">
-      <c r="A143" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B143" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C143" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D143" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E143" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F143" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G143" s="24" t="s">
+      <c r="A143" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B143" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C143" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D143" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E143" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F143" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G143" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="144" ht="17.25" customHeight="1" spans="1:7">
-      <c r="A144" s="28" t="s">
+      <c r="A144" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B144" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C144" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D144" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E144" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F144" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G144" s="24" t="s">
+      <c r="B144" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C144" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D144" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E144" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F144" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G144" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="145" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A145" s="26" t="s">
+      <c r="A145" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="B145" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C145" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D145" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E145" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F145" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G145" s="24" t="s">
+      <c r="B145" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C145" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D145" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E145" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F145" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G145" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="146" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A146" s="26" t="s">
+      <c r="A146" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="B146" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C146" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D146" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E146" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F146" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G146" s="24" t="s">
+      <c r="B146" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C146" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D146" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E146" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F146" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G146" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="147" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A147" s="26" t="s">
+      <c r="A147" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="B147" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C147" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D147" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E147" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F147" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G147" s="24" t="s">
+      <c r="B147" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C147" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D147" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E147" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F147" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G147" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="148" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A148" s="26" t="s">
+      <c r="A148" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="B148" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C148" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D148" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E148" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F148" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G148" s="24" t="s">
+      <c r="B148" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C148" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D148" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E148" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F148" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G148" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="149" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A149" s="26" t="s">
+      <c r="A149" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="B149" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C149" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D149" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E149" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F149" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G149" s="24" t="s">
+      <c r="B149" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C149" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D149" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E149" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F149" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G149" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="150" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A150" s="26" t="s">
+      <c r="A150" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="B150" s="26"/>
-      <c r="C150" s="26"/>
-      <c r="D150" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E150" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F150" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G150" s="24" t="s">
+      <c r="B150" s="37"/>
+      <c r="C150" s="37"/>
+      <c r="D150" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E150" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F150" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G150" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="151" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A151" s="26" t="s">
+      <c r="A151" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="B151" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C151" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D151" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E151" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F151" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G151" s="24" t="s">
+      <c r="B151" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C151" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D151" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E151" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F151" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G151" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="152" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A152" s="26" t="s">
+      <c r="A152" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="B152" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C152" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D152" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E152" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F152" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G152" s="24" t="s">
+      <c r="B152" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C152" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D152" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E152" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F152" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G152" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="153" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A153" s="26" t="s">
+      <c r="A153" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="B153" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C153" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D153" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E153" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F153" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G153" s="24" t="s">
+      <c r="B153" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C153" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D153" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E153" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F153" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G153" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="154" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A154" s="26" t="s">
+      <c r="A154" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="B154" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C154" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D154" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E154" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F154" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G154" s="24" t="s">
+      <c r="B154" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C154" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D154" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E154" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F154" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G154" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="155" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A155" s="26" t="s">
+      <c r="A155" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="B155" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C155" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D155" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E155" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F155" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G155" s="24" t="s">
+      <c r="B155" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C155" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D155" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E155" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F155" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G155" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="156" ht="30.75" customHeight="1" spans="1:7">
-      <c r="A156" s="26" t="s">
+      <c r="A156" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="B156" s="26"/>
-      <c r="C156" s="26"/>
-      <c r="D156" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E156" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F156" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G156" s="24" t="s">
+      <c r="B156" s="37"/>
+      <c r="C156" s="37"/>
+      <c r="D156" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E156" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F156" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G156" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="157" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A157" s="26" t="s">
+      <c r="A157" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="B157" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C157" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D157" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E157" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F157" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G157" s="24" t="s">
+      <c r="B157" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C157" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D157" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E157" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F157" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G157" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="158" ht="282.75" customHeight="1" spans="1:7">
-      <c r="A158" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B158" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C158" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D158" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E158" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F158" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G158" s="24" t="s">
+      <c r="A158" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B158" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C158" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D158" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E158" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F158" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G158" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="1:7">
-      <c r="A159" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B159" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C159" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D159" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E159" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F159" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G159" s="24" t="s">
+      <c r="A159" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B159" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C159" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D159" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E159" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F159" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G159" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="160" ht="16.5" spans="1:7">
-      <c r="A160" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B160" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C160" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D160" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E160" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F160" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G160" s="24" t="s">
+      <c r="A160" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B160" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C160" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D160" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E160" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F160" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G160" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="161" ht="16.5" spans="1:7">
-      <c r="A161" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B161" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C161" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D161" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E161" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F161" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G161" s="24" t="s">
+      <c r="A161" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B161" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C161" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D161" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E161" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F161" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G161" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="1:7">
-      <c r="A162" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B162" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C162" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D162" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E162" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F162" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G162" s="24" t="s">
+      <c r="A162" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B162" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C162" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D162" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E162" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F162" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G162" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="1:7">
-      <c r="A163" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B163" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C163" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D163" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E163" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F163" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G163" s="24" t="s">
+      <c r="A163" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B163" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C163" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D163" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E163" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F163" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G163" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="1:7">
-      <c r="A164" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B164" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C164" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D164" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E164" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F164" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G164" s="24" t="s">
+      <c r="A164" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B164" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C164" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D164" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E164" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F164" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G164" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="165" ht="16.5" spans="1:7">
-      <c r="A165" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B165" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C165" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D165" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E165" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F165" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G165" s="24" t="s">
+      <c r="A165" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B165" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C165" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D165" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E165" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F165" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G165" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="166" ht="16.5" spans="1:7">
-      <c r="A166" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B166" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C166" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D166" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E166" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F166" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G166" s="24" t="s">
+      <c r="A166" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B166" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C166" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D166" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E166" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F166" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G166" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="1:7">
-      <c r="A167" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B167" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C167" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D167" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E167" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F167" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G167" s="24" t="s">
+      <c r="A167" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B167" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C167" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D167" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E167" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F167" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G167" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="168" ht="16.5" spans="1:7">
-      <c r="A168" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B168" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C168" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D168" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E168" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F168" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G168" s="24" t="s">
+      <c r="A168" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B168" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C168" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D168" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E168" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F168" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G168" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="169" ht="16.5" spans="1:7">
-      <c r="A169" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B169" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C169" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D169" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E169" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F169" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G169" s="24" t="s">
+      <c r="A169" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B169" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C169" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D169" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E169" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F169" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G169" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="170" ht="16.5" spans="1:7">
-      <c r="A170" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B170" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C170" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D170" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E170" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F170" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G170" s="24" t="s">
+      <c r="A170" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B170" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C170" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D170" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E170" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F170" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G170" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="171" ht="16.5" spans="1:7">
-      <c r="A171" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B171" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C171" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D171" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E171" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F171" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G171" s="24" t="s">
+      <c r="A171" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B171" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C171" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D171" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E171" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F171" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G171" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="172" ht="16.5" spans="1:7">
-      <c r="A172" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B172" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C172" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D172" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E172" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F172" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G172" s="24" t="s">
+      <c r="A172" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B172" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C172" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D172" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E172" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F172" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G172" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="173" ht="16.5" spans="1:7">
-      <c r="A173" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B173" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C173" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D173" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E173" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F173" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G173" s="24" t="s">
+      <c r="A173" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B173" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C173" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D173" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E173" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F173" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G173" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="174" ht="16.5" spans="1:7">
-      <c r="A174" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B174" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C174" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D174" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E174" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F174" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G174" s="24" t="s">
+      <c r="A174" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B174" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C174" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D174" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E174" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F174" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G174" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="1:7">
-      <c r="A175" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B175" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C175" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D175" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E175" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F175" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G175" s="24" t="s">
+      <c r="A175" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B175" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C175" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D175" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E175" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F175" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G175" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="1:7">
-      <c r="A176" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B176" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C176" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D176" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E176" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F176" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G176" s="24" t="s">
+      <c r="A176" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B176" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C176" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D176" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E176" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F176" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G176" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="1:10">
-      <c r="A177" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B177" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C177" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D177" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E177" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F177" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G177" s="24" t="s">
+      <c r="A177" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B177" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C177" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D177" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E177" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F177" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G177" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="1:10">
-      <c r="A178" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B178" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C178" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D178" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E178" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F178" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G178" s="24" t="s">
+      <c r="A178" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B178" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C178" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D178" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E178" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F178" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G178" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="1:10">
-      <c r="A179" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B179" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C179" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D179" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E179" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F179" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G179" s="24" t="s">
+      <c r="A179" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B179" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C179" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D179" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E179" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F179" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G179" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="1:10">
-      <c r="A180" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B180" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C180" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D180" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E180" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F180" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G180" s="24" t="s">
+      <c r="A180" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B180" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C180" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D180" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E180" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F180" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G180" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="181" ht="16.5" spans="1:10">
-      <c r="A181" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B181" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C181" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D181" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E181" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F181" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G181" s="24" t="s">
+      <c r="A181" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B181" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C181" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D181" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E181" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F181" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G181" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="182" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A182" s="28" t="s">
+      <c r="A182" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B182" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C182" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D182" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E182" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F182" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G182" s="24" t="s">
+      <c r="B182" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C182" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D182" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E182" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F182" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G182" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="183" ht="30.75" customHeight="1" spans="1:10">
-      <c r="A183" s="26" t="s">
+      <c r="A183" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="B183" s="26"/>
-      <c r="C183" s="26"/>
-      <c r="D183" s="26"/>
-      <c r="E183" s="26"/>
-      <c r="F183" s="26"/>
-      <c r="G183" s="26"/>
+      <c r="B183" s="37"/>
+      <c r="C183" s="37"/>
+      <c r="D183" s="37"/>
+      <c r="E183" s="37"/>
+      <c r="F183" s="37"/>
+      <c r="G183" s="37"/>
     </row>
     <row r="184" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A184" s="28" t="s">
+      <c r="A184" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="B184" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C184" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D184" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E184" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F184" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G184" s="24" t="s">
+      <c r="B184" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C184" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D184" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E184" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F184" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G184" s="35" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" spans="1:10">
-      <c r="A185" s="24" t="s">
+      <c r="A185" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="B185" s="24" t="s">
+      <c r="B185" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="C185" s="24" t="s">
+      <c r="C185" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D185" s="24" t="s">
+      <c r="D185" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="E185" s="24" t="s">
+      <c r="E185" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="F185" s="24" t="s">
+      <c r="F185" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="G185" s="24" t="s">
+      <c r="G185" s="35" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="186" ht="66.75" customHeight="1" spans="1:10">
-      <c r="A186" s="30" t="s">
+      <c r="A186" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B186" s="31" t="s">
+      <c r="B186" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="C186" s="31" t="s">
+      <c r="C186" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="D186" s="31" t="s">
+      <c r="D186" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="E186" s="31" t="s">
+      <c r="E186" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="F186" s="31" t="s">
+      <c r="F186" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="G186" s="31" t="s">
+      <c r="G186" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="H186" s="31"/>
-      <c r="I186" s="31"/>
+      <c r="H186" s="42"/>
+      <c r="I186" s="42"/>
     </row>
     <row r="187" ht="41.25" customHeight="1" spans="1:10">
-      <c r="A187" s="30" t="s">
+      <c r="A187" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B187" s="31" t="s">
+      <c r="B187" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="C187" s="31">
+      <c r="C187" s="42">
         <v>15</v>
       </c>
-      <c r="D187" s="31" t="s">
+      <c r="D187" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="E187" s="31" t="s">
+      <c r="E187" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="F187" s="31" t="s">
+      <c r="F187" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="G187" s="31" t="s">
+      <c r="G187" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="H187" s="31"/>
+      <c r="H187" s="42"/>
     </row>
     <row r="188" ht="54" customHeight="1" spans="1:10">
-      <c r="A188" s="30" t="s">
+      <c r="A188" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="B188" s="31" t="s">
+      <c r="B188" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="C188" s="31">
+      <c r="C188" s="42">
         <v>15</v>
       </c>
-      <c r="D188" s="31" t="s">
+      <c r="D188" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="E188" s="31" t="s">
+      <c r="E188" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="F188" s="31" t="s">
+      <c r="F188" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G188" s="32" t="s">
+      <c r="G188" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="H188" s="32"/>
-      <c r="I188" s="32"/>
-      <c r="J188" s="32"/>
+      <c r="H188" s="43"/>
+      <c r="I188" s="43"/>
+      <c r="J188" s="43"/>
     </row>
     <row r="189" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A189" s="28" t="s">
+      <c r="A189" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="B189" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C189" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D189" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E189" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F189" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G189" s="31" t="s">
+      <c r="B189" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C189" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D189" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E189" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F189" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G189" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1" spans="1:10">
-      <c r="A190" s="24" t="s">
+      <c r="A190" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="B190" s="24" t="s">
+      <c r="B190" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="C190" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D190" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E190" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F190" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G190" s="31" t="s">
+      <c r="C190" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D190" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E190" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F190" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G190" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1" spans="1:10">
-      <c r="A191" s="30" t="s">
+      <c r="A191" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="B191" s="31" t="s">
+      <c r="B191" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="C191" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D191" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E191" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F191" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G191" s="31" t="s">
+      <c r="C191" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D191" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E191" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F191" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G191" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="192" ht="54" customHeight="1" spans="1:10">
-      <c r="A192" s="30" t="s">
+      <c r="A192" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="B192" s="31" t="s">
+      <c r="B192" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="C192" s="31"/>
-      <c r="D192" s="31"/>
-      <c r="E192" s="31"/>
-      <c r="F192" s="31"/>
-      <c r="G192" s="31" t="s">
+      <c r="C192" s="42"/>
+      <c r="D192" s="42"/>
+      <c r="E192" s="42"/>
+      <c r="F192" s="42"/>
+      <c r="G192" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="193" ht="54" customHeight="1" spans="1:7">
-      <c r="A193" s="30" t="s">
+      <c r="A193" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="B193" s="31" t="s">
+      <c r="B193" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="C193" s="31"/>
-      <c r="D193" s="31"/>
-      <c r="E193" s="31"/>
-      <c r="F193" s="31"/>
-      <c r="G193" s="31" t="s">
+      <c r="C193" s="42"/>
+      <c r="D193" s="42"/>
+      <c r="E193" s="42"/>
+      <c r="F193" s="42"/>
+      <c r="G193" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="194" ht="41.25" customHeight="1" spans="1:7">
-      <c r="A194" s="30" t="s">
+      <c r="A194" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="B194" s="31" t="s">
+      <c r="B194" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="C194" s="31"/>
-      <c r="D194" s="31"/>
-      <c r="E194" s="31"/>
-      <c r="F194" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G194" s="31" t="s">
+      <c r="C194" s="42"/>
+      <c r="D194" s="42"/>
+      <c r="E194" s="42"/>
+      <c r="F194" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G194" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="195" ht="27.75" customHeight="1" spans="1:7">
-      <c r="A195" s="30" t="s">
+      <c r="A195" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="B195" s="31" t="s">
+      <c r="B195" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="C195" s="31"/>
-      <c r="D195" s="31"/>
-      <c r="E195" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F195" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G195" s="31" t="s">
+      <c r="C195" s="42"/>
+      <c r="D195" s="42"/>
+      <c r="E195" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F195" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G195" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" spans="1:7">
-      <c r="A196" s="30" t="s">
+      <c r="A196" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="B196" s="31" t="s">
+      <c r="B196" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="C196" s="31"/>
-      <c r="D196" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E196" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F196" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G196" s="31" t="s">
+      <c r="C196" s="42"/>
+      <c r="D196" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E196" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F196" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G196" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="197" ht="41.25" customHeight="1" spans="1:7">
-      <c r="A197" s="30" t="s">
+      <c r="A197" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="B197" s="31" t="s">
+      <c r="B197" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="C197" s="31"/>
-      <c r="D197" s="31"/>
-      <c r="E197" s="31"/>
-      <c r="F197" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G197" s="31" t="s">
+      <c r="C197" s="42"/>
+      <c r="D197" s="42"/>
+      <c r="E197" s="42"/>
+      <c r="F197" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G197" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="198" ht="41.25" customHeight="1" spans="1:7">
-      <c r="A198" s="30" t="s">
+      <c r="A198" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="B198" s="31" t="s">
+      <c r="B198" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="C198" s="31"/>
-      <c r="D198" s="31"/>
-      <c r="E198" s="31"/>
-      <c r="F198" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G198" s="31" t="s">
+      <c r="C198" s="42"/>
+      <c r="D198" s="42"/>
+      <c r="E198" s="42"/>
+      <c r="F198" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G198" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="199" ht="41.25" customHeight="1" spans="1:7">
-      <c r="A199" s="30" t="s">
+      <c r="A199" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="B199" s="31" t="s">
+      <c r="B199" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="C199" s="31"/>
-      <c r="D199" s="31"/>
-      <c r="E199" s="31"/>
-      <c r="F199" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G199" s="31" t="s">
+      <c r="C199" s="42"/>
+      <c r="D199" s="42"/>
+      <c r="E199" s="42"/>
+      <c r="F199" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G199" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="200" ht="41.25" customHeight="1" spans="1:7">
-      <c r="A200" s="30" t="s">
+      <c r="A200" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="B200" s="31" t="s">
+      <c r="B200" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="C200" s="31"/>
-      <c r="D200" s="31"/>
-      <c r="E200" s="31"/>
-      <c r="F200" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G200" s="31" t="s">
+      <c r="C200" s="42"/>
+      <c r="D200" s="42"/>
+      <c r="E200" s="42"/>
+      <c r="F200" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G200" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="201" ht="17.25" customHeight="1" spans="1:7">
-      <c r="A201" s="28" t="s">
+      <c r="A201" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B201" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C201" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D201" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E201" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F201" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G201" s="31" t="s">
+      <c r="B201" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C201" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D201" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E201" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F201" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G201" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" spans="1:7">
-      <c r="A202" s="24" t="s">
+      <c r="A202" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="B202" s="24" t="s">
+      <c r="B202" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="C202" s="24" t="s">
+      <c r="C202" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="D202" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E202" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F202" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G202" s="31" t="s">
+      <c r="D202" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E202" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F202" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G202" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" spans="1:7">
-      <c r="A203" s="30" t="s">
+      <c r="A203" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="B203" s="31" t="s">
+      <c r="B203" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="C203" s="31" t="s">
+      <c r="C203" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="D203" s="31"/>
-      <c r="E203" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F203" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G203" s="31" t="s">
+      <c r="D203" s="42"/>
+      <c r="E203" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F203" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G203" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="204" ht="27.75" customHeight="1" spans="1:7">
-      <c r="A204" s="30" t="s">
+      <c r="A204" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="B204" s="31" t="s">
+      <c r="B204" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="C204" s="31" t="s">
+      <c r="C204" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="D204" s="31"/>
-      <c r="E204" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F204" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G204" s="31" t="s">
+      <c r="D204" s="42"/>
+      <c r="E204" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F204" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G204" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1" spans="1:7">
-      <c r="A205" s="30" t="s">
+      <c r="A205" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="B205" s="31" t="s">
+      <c r="B205" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="C205" s="31" t="s">
+      <c r="C205" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="D205" s="31"/>
-      <c r="E205" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F205" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G205" s="31" t="s">
+      <c r="D205" s="42"/>
+      <c r="E205" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F205" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G205" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1" spans="1:7">
-      <c r="A206" s="30" t="s">
+      <c r="A206" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="B206" s="31" t="s">
+      <c r="B206" s="42" t="s">
         <v>147</v>
       </c>
-      <c r="C206" s="31" t="s">
+      <c r="C206" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="D206" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E206" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F206" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G206" s="31" t="s">
+      <c r="D206" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E206" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F206" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G206" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="207" ht="17.25" customHeight="1" spans="1:7">
-      <c r="A207" s="28" t="s">
+      <c r="A207" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="B207" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C207" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D207" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E207" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F207" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G207" s="31" t="s">
+      <c r="B207" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C207" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D207" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E207" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F207" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G207" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="208" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A208" s="26" t="s">
+      <c r="A208" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="B208" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C208" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D208" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E208" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F208" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G208" s="31" t="s">
+      <c r="B208" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C208" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D208" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E208" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F208" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G208" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="209" ht="30.75" customHeight="1" spans="1:7">
-      <c r="A209" s="26" t="s">
+      <c r="A209" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="B209" s="26"/>
-      <c r="C209" s="26"/>
-      <c r="D209" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E209" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F209" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G209" s="31" t="s">
+      <c r="B209" s="37"/>
+      <c r="C209" s="37"/>
+      <c r="D209" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E209" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F209" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G209" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="210" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A210" s="26" t="s">
+      <c r="A210" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="B210" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C210" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D210" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E210" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F210" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G210" s="31" t="s">
+      <c r="B210" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C210" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D210" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E210" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F210" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G210" s="42" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6827,15 +6860,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:7">
       <c r="A2" s="2" t="s">
@@ -7060,14 +7093,14 @@
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
       <c r="G12" s="2" t="s">
         <v>1</v>
       </c>
@@ -7505,12 +7538,12 @@
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:7">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
       <c r="E30" s="2" t="s">
         <v>1</v>
       </c>
@@ -7688,12 +7721,12 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:8">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
       <c r="E38" s="2" t="s">
         <v>1</v>
       </c>
@@ -7804,13 +7837,13 @@
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+      <c r="B44" s="33"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33"/>
       <c r="F44" s="2" t="s">
         <v>1</v>
       </c>
@@ -8044,14 +8077,14 @@
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+      <c r="B54" s="33"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="33"/>
       <c r="G54" s="2" t="s">
         <v>1</v>
       </c>
@@ -8247,14 +8280,14 @@
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
       <c r="G63" s="2" t="s">
         <v>1</v>
       </c>
@@ -8444,13 +8477,13 @@
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
+      <c r="B71" s="33"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="33"/>
       <c r="F71" s="7" t="s">
         <v>1</v>
       </c>
@@ -8649,12 +8682,12 @@
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="33" t="s">
         <v>237</v>
       </c>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
+      <c r="B80" s="33"/>
+      <c r="C80" s="33"/>
+      <c r="D80" s="33"/>
       <c r="E80" s="11" t="s">
         <v>1</v>
       </c>
@@ -8850,12 +8883,12 @@
       </c>
     </row>
     <row r="90" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
+      <c r="B90" s="33"/>
+      <c r="C90" s="33"/>
+      <c r="D90" s="33"/>
       <c r="E90" s="11" t="s">
         <v>1</v>
       </c>
@@ -9159,12 +9192,12 @@
       </c>
     </row>
     <row r="104" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
+      <c r="B104" s="33"/>
+      <c r="C104" s="33"/>
+      <c r="D104" s="33"/>
       <c r="E104" s="11" t="s">
         <v>1</v>
       </c>
@@ -9346,14 +9379,14 @@
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" spans="1:9">
-      <c r="A113" s="1" t="s">
+      <c r="A113" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="33"/>
+      <c r="D113" s="33"/>
+      <c r="E113" s="33"/>
+      <c r="F113" s="33"/>
       <c r="G113" s="2" t="s">
         <v>1</v>
       </c>
@@ -9477,11 +9510,11 @@
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" spans="1:9">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
+      <c r="B119" s="33"/>
+      <c r="C119" s="33"/>
       <c r="D119" s="19" t="s">
         <v>1</v>
       </c>
@@ -9607,12 +9640,12 @@
       </c>
     </row>
     <row r="125" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A125" s="1" t="s">
+      <c r="A125" s="33" t="s">
         <v>272</v>
       </c>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
+      <c r="B125" s="33"/>
+      <c r="C125" s="33"/>
+      <c r="D125" s="33"/>
       <c r="E125" s="19" t="s">
         <v>1</v>
       </c>
